--- a/data/evidence/ft024_cobalt_cerium_database.xlsx
+++ b/data/evidence/ft024_cobalt_cerium_database.xlsx
@@ -2,9 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" r:id="Ra1063a26a35543d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medições" sheetId="2" r:id="R131619710c5d4b66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critérios" sheetId="3" r:id="Re2a27daf4f5b4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumo" sheetId="1" r:id="R07686ef0d83345cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Medições" sheetId="2" r:id="Rccf96e6311f14af2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Critérios" sheetId="3" r:id="R3358ff260f4640cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Evidência parcial" sheetId="6" r:id="Rf7bb3f2d151d47ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontes parciais" sheetId="7" r:id="R23084e10cc2942f6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -19,7 +21,7 @@
     <x:numFmt numFmtId="200" formatCode="0.000"/>
     <x:numFmt numFmtId="201" formatCode="0.000000"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -50,8 +52,14 @@
       <x:sz val="9"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -68,6 +76,16 @@
         <x:fgColor rgb="FFF4B183"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17324D"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border>
@@ -81,7 +99,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -104,11 +122,120 @@
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FT024PartialEvidence" displayName="FT024PartialEvidence" ref="A1:X62" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="24">
+    <x:tableColumn id="1" name="measurement_id"/>
+    <x:tableColumn id="2" name="run_id"/>
+    <x:tableColumn id="3" name="dataset_id"/>
+    <x:tableColumn id="4" name="catalyst_id"/>
+    <x:tableColumn id="5" name="catalyst_composition"/>
+    <x:tableColumn id="6" name="support"/>
+    <x:tableColumn id="7" name="preparation_method"/>
+    <x:tableColumn id="8" name="temperature_c"/>
+    <x:tableColumn id="9" name="pressure_bar"/>
+    <x:tableColumn id="10" name="h2_co_ratio"/>
+    <x:tableColumn id="11" name="ghsv_h_inv"/>
+    <x:tableColumn id="12" name="response_name"/>
+    <x:tableColumn id="13" name="response_value"/>
+    <x:tableColumn id="14" name="response_unit"/>
+    <x:tableColumn id="15" name="value_qualifier"/>
+    <x:tableColumn id="16" name="measurement_uncertainty"/>
+    <x:tableColumn id="17" name="source_reference"/>
+    <x:tableColumn id="18" name="source_locator"/>
+    <x:tableColumn id="19" name="source_url"/>
+    <x:tableColumn id="20" name="evidence_type"/>
+    <x:tableColumn id="21" name="compatibility_class"/>
+    <x:tableColumn id="22" name="external_validation_eligible"/>
+    <x:tableColumn id="23" name="exclusion_reason"/>
+    <x:tableColumn id="24" name="extraction_note"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="FT024PartialSources" displayName="FT024PartialSources" ref="A1:K18" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="11">
+    <x:tableColumn id="1" name="source_id"/>
+    <x:tableColumn id="2" name="reference"/>
+    <x:tableColumn id="3" name="document_type"/>
+    <x:tableColumn id="4" name="institution_or_journal"/>
+    <x:tableColumn id="5" name="catalyst_scope"/>
+    <x:tableColumn id="6" name="numeric_extraction_status"/>
+    <x:tableColumn id="7" name="included_measurements"/>
+    <x:tableColumn id="8" name="priority"/>
+    <x:tableColumn id="9" name="validation_role"/>
+    <x:tableColumn id="10" name="source_url"/>
+    <x:tableColumn id="11" name="note"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -368,6 +495,14 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="5" t="str">
+        <x:v>Medições contextuais parciais</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="n">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
     <x:row r="11">
       <x:c r="A11" s="7" t="str">
         <x:v>Limite científico</x:v>
@@ -26097,4 +26232,5283 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="24" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="24" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="24" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="24" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="24" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="24" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="24" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="25" t="str">
+        <x:v>measurement_id</x:v>
+      </x:c>
+      <x:c r="B1" s="25" t="str">
+        <x:v>run_id</x:v>
+      </x:c>
+      <x:c r="C1" s="25" t="str">
+        <x:v>dataset_id</x:v>
+      </x:c>
+      <x:c r="D1" s="25" t="str">
+        <x:v>catalyst_id</x:v>
+      </x:c>
+      <x:c r="E1" s="25" t="str">
+        <x:v>catalyst_composition</x:v>
+      </x:c>
+      <x:c r="F1" s="25" t="str">
+        <x:v>support</x:v>
+      </x:c>
+      <x:c r="G1" s="25" t="str">
+        <x:v>preparation_method</x:v>
+      </x:c>
+      <x:c r="H1" s="25" t="str">
+        <x:v>temperature_c</x:v>
+      </x:c>
+      <x:c r="I1" s="25" t="str">
+        <x:v>pressure_bar</x:v>
+      </x:c>
+      <x:c r="J1" s="25" t="str">
+        <x:v>h2_co_ratio</x:v>
+      </x:c>
+      <x:c r="K1" s="25" t="str">
+        <x:v>ghsv_h_inv</x:v>
+      </x:c>
+      <x:c r="L1" s="25" t="str">
+        <x:v>response_name</x:v>
+      </x:c>
+      <x:c r="M1" s="25" t="str">
+        <x:v>response_value</x:v>
+      </x:c>
+      <x:c r="N1" s="25" t="str">
+        <x:v>response_unit</x:v>
+      </x:c>
+      <x:c r="O1" s="25" t="str">
+        <x:v>value_qualifier</x:v>
+      </x:c>
+      <x:c r="P1" s="25" t="str">
+        <x:v>measurement_uncertainty</x:v>
+      </x:c>
+      <x:c r="Q1" s="25" t="str">
+        <x:v>source_reference</x:v>
+      </x:c>
+      <x:c r="R1" s="25" t="str">
+        <x:v>source_locator</x:v>
+      </x:c>
+      <x:c r="S1" s="25" t="str">
+        <x:v>source_url</x:v>
+      </x:c>
+      <x:c r="T1" s="25" t="str">
+        <x:v>evidence_type</x:v>
+      </x:c>
+      <x:c r="U1" s="25" t="str">
+        <x:v>compatibility_class</x:v>
+      </x:c>
+      <x:c r="V1" s="25" t="str">
+        <x:v>external_validation_eligible</x:v>
+      </x:c>
+      <x:c r="W1" s="25" t="str">
+        <x:v>exclusion_reason</x:v>
+      </x:c>
+      <x:c r="X1" s="25" t="str">
+        <x:v>extraction_note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="20" t="str">
+        <x:v>mirzaei2007-t1-100Co_0Ce-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B2" s="20" t="str">
+        <x:v>mirzaei2007-100Co_0Ce</x:v>
+      </x:c>
+      <x:c r="C2" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D2" s="20" t="str">
+        <x:v>Mirzaei2007_100Co_0Ce</x:v>
+      </x:c>
+      <x:c r="E2" s="20" t="str">
+        <x:v>100mol%Co/0mol%Ce</x:v>
+      </x:c>
+      <x:c r="F2" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G2" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H2" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I2" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J2" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K2" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L2" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M2" s="20" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N2" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O2" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P2" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q2" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R2" s="20" t="str">
+        <x:v>Table 1; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S2" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T2" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U2" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V2" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W2" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X2" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="20" t="str">
+        <x:v>mirzaei2007-t1-100Co_0Ce-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B3" s="20" t="str">
+        <x:v>mirzaei2007-100Co_0Ce</x:v>
+      </x:c>
+      <x:c r="C3" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D3" s="20" t="str">
+        <x:v>Mirzaei2007_100Co_0Ce</x:v>
+      </x:c>
+      <x:c r="E3" s="20" t="str">
+        <x:v>100mol%Co/0mol%Ce</x:v>
+      </x:c>
+      <x:c r="F3" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G3" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H3" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I3" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J3" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K3" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L3" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M3" s="20" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N3" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O3" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P3" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q3" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R3" s="20" t="str">
+        <x:v>Table 1; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S3" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T3" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U3" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V3" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W3" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X3" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="20" t="str">
+        <x:v>mirzaei2007-t1-100Co_0Ce-precursor</x:v>
+      </x:c>
+      <x:c r="B4" s="20" t="str">
+        <x:v>mirzaei2007-100Co_0Ce</x:v>
+      </x:c>
+      <x:c r="C4" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D4" s="20" t="str">
+        <x:v>Mirzaei2007_100Co_0Ce</x:v>
+      </x:c>
+      <x:c r="E4" s="20" t="str">
+        <x:v>100mol%Co/0mol%Ce</x:v>
+      </x:c>
+      <x:c r="F4" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G4" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H4" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I4" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J4" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K4" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L4" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M4" s="20" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="N4" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O4" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P4" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q4" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R4" s="20" t="str">
+        <x:v>Table 1; precursor</x:v>
+      </x:c>
+      <x:c r="S4" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T4" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U4" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V4" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W4" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X4" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="20" t="str">
+        <x:v>mirzaei2007-t1-80Co_20Ce-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B5" s="20" t="str">
+        <x:v>mirzaei2007-80Co_20Ce</x:v>
+      </x:c>
+      <x:c r="C5" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D5" s="20" t="str">
+        <x:v>Mirzaei2007_80Co_20Ce</x:v>
+      </x:c>
+      <x:c r="E5" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F5" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G5" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H5" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I5" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J5" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K5" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L5" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M5" s="20" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="N5" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O5" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P5" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q5" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R5" s="20" t="str">
+        <x:v>Table 1; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S5" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T5" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U5" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V5" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W5" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X5" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="20" t="str">
+        <x:v>mirzaei2007-t1-80Co_20Ce-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B6" s="20" t="str">
+        <x:v>mirzaei2007-80Co_20Ce</x:v>
+      </x:c>
+      <x:c r="C6" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D6" s="20" t="str">
+        <x:v>Mirzaei2007_80Co_20Ce</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G6" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I6" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J6" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K6" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L6" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M6" s="20" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N6" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O6" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P6" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q6" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R6" s="20" t="str">
+        <x:v>Table 1; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S6" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T6" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U6" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V6" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W6" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X6" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="20" t="str">
+        <x:v>mirzaei2007-t1-80Co_20Ce-precursor</x:v>
+      </x:c>
+      <x:c r="B7" s="20" t="str">
+        <x:v>mirzaei2007-80Co_20Ce</x:v>
+      </x:c>
+      <x:c r="C7" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D7" s="20" t="str">
+        <x:v>Mirzaei2007_80Co_20Ce</x:v>
+      </x:c>
+      <x:c r="E7" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F7" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G7" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H7" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I7" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J7" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K7" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L7" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M7" s="20" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N7" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O7" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P7" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q7" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R7" s="20" t="str">
+        <x:v>Table 1; precursor</x:v>
+      </x:c>
+      <x:c r="S7" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T7" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U7" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V7" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W7" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X7" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="20" t="str">
+        <x:v>mirzaei2007-t1-60Co_40Ce-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B8" s="20" t="str">
+        <x:v>mirzaei2007-60Co_40Ce</x:v>
+      </x:c>
+      <x:c r="C8" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D8" s="20" t="str">
+        <x:v>Mirzaei2007_60Co_40Ce</x:v>
+      </x:c>
+      <x:c r="E8" s="20" t="str">
+        <x:v>60mol%Co/40mol%Ce</x:v>
+      </x:c>
+      <x:c r="F8" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G8" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H8" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I8" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J8" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K8" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L8" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M8" s="20" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="N8" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O8" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P8" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q8" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R8" s="20" t="str">
+        <x:v>Table 1; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S8" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T8" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U8" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V8" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W8" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X8" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="20" t="str">
+        <x:v>mirzaei2007-t1-60Co_40Ce-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B9" s="20" t="str">
+        <x:v>mirzaei2007-60Co_40Ce</x:v>
+      </x:c>
+      <x:c r="C9" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D9" s="20" t="str">
+        <x:v>Mirzaei2007_60Co_40Ce</x:v>
+      </x:c>
+      <x:c r="E9" s="20" t="str">
+        <x:v>60mol%Co/40mol%Ce</x:v>
+      </x:c>
+      <x:c r="F9" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G9" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H9" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I9" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J9" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K9" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L9" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M9" s="20" t="n">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="N9" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O9" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P9" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q9" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R9" s="20" t="str">
+        <x:v>Table 1; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S9" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T9" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U9" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V9" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W9" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X9" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="20" t="str">
+        <x:v>mirzaei2007-t1-60Co_40Ce-precursor</x:v>
+      </x:c>
+      <x:c r="B10" s="20" t="str">
+        <x:v>mirzaei2007-60Co_40Ce</x:v>
+      </x:c>
+      <x:c r="C10" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D10" s="20" t="str">
+        <x:v>Mirzaei2007_60Co_40Ce</x:v>
+      </x:c>
+      <x:c r="E10" s="20" t="str">
+        <x:v>60mol%Co/40mol%Ce</x:v>
+      </x:c>
+      <x:c r="F10" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G10" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H10" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I10" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J10" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K10" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L10" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M10" s="20" t="n">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="N10" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O10" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P10" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q10" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R10" s="20" t="str">
+        <x:v>Table 1; precursor</x:v>
+      </x:c>
+      <x:c r="S10" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T10" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U10" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V10" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W10" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X10" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="20" t="str">
+        <x:v>mirzaei2007-t1-50Co_50Ce-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B11" s="20" t="str">
+        <x:v>mirzaei2007-50Co_50Ce</x:v>
+      </x:c>
+      <x:c r="C11" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D11" s="20" t="str">
+        <x:v>Mirzaei2007_50Co_50Ce</x:v>
+      </x:c>
+      <x:c r="E11" s="20" t="str">
+        <x:v>50mol%Co/50mol%Ce</x:v>
+      </x:c>
+      <x:c r="F11" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G11" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H11" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I11" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J11" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L11" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M11" s="20" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N11" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O11" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P11" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q11" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R11" s="20" t="str">
+        <x:v>Table 1; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S11" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T11" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U11" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V11" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W11" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X11" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="20" t="str">
+        <x:v>mirzaei2007-t1-50Co_50Ce-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B12" s="20" t="str">
+        <x:v>mirzaei2007-50Co_50Ce</x:v>
+      </x:c>
+      <x:c r="C12" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D12" s="20" t="str">
+        <x:v>Mirzaei2007_50Co_50Ce</x:v>
+      </x:c>
+      <x:c r="E12" s="20" t="str">
+        <x:v>50mol%Co/50mol%Ce</x:v>
+      </x:c>
+      <x:c r="F12" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G12" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H12" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I12" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J12" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K12" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L12" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M12" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N12" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O12" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P12" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q12" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R12" s="20" t="str">
+        <x:v>Table 1; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S12" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T12" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U12" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V12" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W12" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X12" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="20" t="str">
+        <x:v>mirzaei2007-t1-50Co_50Ce-precursor</x:v>
+      </x:c>
+      <x:c r="B13" s="20" t="str">
+        <x:v>mirzaei2007-50Co_50Ce</x:v>
+      </x:c>
+      <x:c r="C13" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D13" s="20" t="str">
+        <x:v>Mirzaei2007_50Co_50Ce</x:v>
+      </x:c>
+      <x:c r="E13" s="20" t="str">
+        <x:v>50mol%Co/50mol%Ce</x:v>
+      </x:c>
+      <x:c r="F13" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G13" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H13" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I13" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J13" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K13" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L13" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M13" s="20" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N13" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O13" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P13" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q13" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R13" s="20" t="str">
+        <x:v>Table 1; precursor</x:v>
+      </x:c>
+      <x:c r="S13" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T13" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U13" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V13" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W13" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X13" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="20" t="str">
+        <x:v>mirzaei2007-t1-40Co_60Ce-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B14" s="20" t="str">
+        <x:v>mirzaei2007-40Co_60Ce</x:v>
+      </x:c>
+      <x:c r="C14" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D14" s="20" t="str">
+        <x:v>Mirzaei2007_40Co_60Ce</x:v>
+      </x:c>
+      <x:c r="E14" s="20" t="str">
+        <x:v>40mol%Co/60mol%Ce</x:v>
+      </x:c>
+      <x:c r="F14" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G14" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H14" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I14" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J14" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K14" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L14" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M14" s="20" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="N14" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O14" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P14" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q14" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R14" s="20" t="str">
+        <x:v>Table 1; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S14" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T14" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U14" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V14" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W14" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X14" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="20" t="str">
+        <x:v>mirzaei2007-t1-40Co_60Ce-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B15" s="20" t="str">
+        <x:v>mirzaei2007-40Co_60Ce</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D15" s="20" t="str">
+        <x:v>Mirzaei2007_40Co_60Ce</x:v>
+      </x:c>
+      <x:c r="E15" s="20" t="str">
+        <x:v>40mol%Co/60mol%Ce</x:v>
+      </x:c>
+      <x:c r="F15" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G15" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H15" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I15" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J15" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K15" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L15" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M15" s="20" t="n">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="N15" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O15" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P15" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q15" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R15" s="20" t="str">
+        <x:v>Table 1; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S15" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T15" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U15" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V15" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W15" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X15" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="20" t="str">
+        <x:v>mirzaei2007-t1-40Co_60Ce-precursor</x:v>
+      </x:c>
+      <x:c r="B16" s="20" t="str">
+        <x:v>mirzaei2007-40Co_60Ce</x:v>
+      </x:c>
+      <x:c r="C16" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D16" s="20" t="str">
+        <x:v>Mirzaei2007_40Co_60Ce</x:v>
+      </x:c>
+      <x:c r="E16" s="20" t="str">
+        <x:v>40mol%Co/60mol%Ce</x:v>
+      </x:c>
+      <x:c r="F16" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G16" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H16" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I16" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J16" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K16" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L16" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M16" s="20" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="N16" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O16" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P16" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q16" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R16" s="20" t="str">
+        <x:v>Table 1; precursor</x:v>
+      </x:c>
+      <x:c r="S16" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T16" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U16" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V16" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W16" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X16" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="20" t="str">
+        <x:v>mirzaei2007-t1-20Co_80Ce-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B17" s="20" t="str">
+        <x:v>mirzaei2007-20Co_80Ce</x:v>
+      </x:c>
+      <x:c r="C17" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D17" s="20" t="str">
+        <x:v>Mirzaei2007_20Co_80Ce</x:v>
+      </x:c>
+      <x:c r="E17" s="20" t="str">
+        <x:v>20mol%Co/80mol%Ce</x:v>
+      </x:c>
+      <x:c r="F17" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G17" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H17" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I17" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J17" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K17" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L17" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M17" s="20" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="N17" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O17" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P17" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q17" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R17" s="20" t="str">
+        <x:v>Table 1; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S17" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T17" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U17" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V17" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W17" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X17" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="20" t="str">
+        <x:v>mirzaei2007-t1-20Co_80Ce-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B18" s="20" t="str">
+        <x:v>mirzaei2007-20Co_80Ce</x:v>
+      </x:c>
+      <x:c r="C18" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D18" s="20" t="str">
+        <x:v>Mirzaei2007_20Co_80Ce</x:v>
+      </x:c>
+      <x:c r="E18" s="20" t="str">
+        <x:v>20mol%Co/80mol%Ce</x:v>
+      </x:c>
+      <x:c r="F18" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G18" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H18" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I18" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J18" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K18" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L18" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M18" s="20" t="n">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="N18" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O18" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P18" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q18" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R18" s="20" t="str">
+        <x:v>Table 1; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S18" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T18" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U18" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V18" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W18" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X18" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="20" t="str">
+        <x:v>mirzaei2007-t1-20Co_80Ce-precursor</x:v>
+      </x:c>
+      <x:c r="B19" s="20" t="str">
+        <x:v>mirzaei2007-20Co_80Ce</x:v>
+      </x:c>
+      <x:c r="C19" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D19" s="20" t="str">
+        <x:v>Mirzaei2007_20Co_80Ce</x:v>
+      </x:c>
+      <x:c r="E19" s="20" t="str">
+        <x:v>20mol%Co/80mol%Ce</x:v>
+      </x:c>
+      <x:c r="F19" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G19" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H19" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I19" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J19" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K19" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L19" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M19" s="20" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="N19" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O19" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P19" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q19" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R19" s="20" t="str">
+        <x:v>Table 1; precursor</x:v>
+      </x:c>
+      <x:c r="S19" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T19" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U19" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V19" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W19" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X19" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="20" t="str">
+        <x:v>mirzaei2007-t1-0Co_100Ce-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B20" s="20" t="str">
+        <x:v>mirzaei2007-0Co_100Ce</x:v>
+      </x:c>
+      <x:c r="C20" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D20" s="20" t="str">
+        <x:v>Mirzaei2007_0Co_100Ce</x:v>
+      </x:c>
+      <x:c r="E20" s="20" t="str">
+        <x:v>0mol%Co/100mol%Ce</x:v>
+      </x:c>
+      <x:c r="F20" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G20" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H20" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I20" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J20" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K20" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L20" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M20" s="20" t="n">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="N20" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O20" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P20" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q20" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R20" s="20" t="str">
+        <x:v>Table 1; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S20" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T20" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U20" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V20" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W20" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X20" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="20" t="str">
+        <x:v>mirzaei2007-t1-0Co_100Ce-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B21" s="20" t="str">
+        <x:v>mirzaei2007-0Co_100Ce</x:v>
+      </x:c>
+      <x:c r="C21" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D21" s="20" t="str">
+        <x:v>Mirzaei2007_0Co_100Ce</x:v>
+      </x:c>
+      <x:c r="E21" s="20" t="str">
+        <x:v>0mol%Co/100mol%Ce</x:v>
+      </x:c>
+      <x:c r="F21" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G21" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H21" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I21" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J21" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K21" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L21" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M21" s="20" t="n">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="N21" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O21" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P21" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q21" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R21" s="20" t="str">
+        <x:v>Table 1; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S21" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T21" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U21" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V21" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W21" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X21" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="20" t="str">
+        <x:v>mirzaei2007-t1-0Co_100Ce-precursor</x:v>
+      </x:c>
+      <x:c r="B22" s="20" t="str">
+        <x:v>mirzaei2007-0Co_100Ce</x:v>
+      </x:c>
+      <x:c r="C22" s="20" t="str">
+        <x:v>mirzaei2007_table1</x:v>
+      </x:c>
+      <x:c r="D22" s="20" t="str">
+        <x:v>Mirzaei2007_0Co_100Ce</x:v>
+      </x:c>
+      <x:c r="E22" s="20" t="str">
+        <x:v>0mol%Co/100mol%Ce</x:v>
+      </x:c>
+      <x:c r="F22" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G22" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H22" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I22" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J22" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K22" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L22" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M22" s="20" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N22" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O22" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P22" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q22" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R22" s="20" t="str">
+        <x:v>Table 1; precursor</x:v>
+      </x:c>
+      <x:c r="S22" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T22" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U22" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V22" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W22" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X22" s="20" t="str">
+        <x:v>BET value; catalytic condition is the screening condition associated with the series</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="20" t="str">
+        <x:v>mirzaei2007-t2-age0-precursor</x:v>
+      </x:c>
+      <x:c r="B23" s="20" t="str">
+        <x:v>mirzaei2007-age0</x:v>
+      </x:c>
+      <x:c r="C23" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D23" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E23" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F23" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G23" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H23" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I23" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J23" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K23" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L23" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M23" s="20" t="n">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="N23" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O23" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P23" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q23" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R23" s="20" t="str">
+        <x:v>Table 2; ageing=0 h; precursor</x:v>
+      </x:c>
+      <x:c r="S23" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T23" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U23" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V23" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W23" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X23" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="20" t="str">
+        <x:v>mirzaei2007-t2-age0-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B24" s="20" t="str">
+        <x:v>mirzaei2007-age0</x:v>
+      </x:c>
+      <x:c r="C24" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D24" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E24" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F24" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G24" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H24" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I24" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J24" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K24" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L24" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M24" s="20" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="N24" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O24" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P24" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q24" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R24" s="20" t="str">
+        <x:v>Table 2; ageing=0 h; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S24" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T24" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U24" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V24" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W24" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X24" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="20" t="str">
+        <x:v>mirzaei2007-t2-age0-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B25" s="20" t="str">
+        <x:v>mirzaei2007-age0</x:v>
+      </x:c>
+      <x:c r="C25" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D25" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E25" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F25" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G25" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H25" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I25" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J25" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K25" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L25" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M25" s="20" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N25" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O25" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P25" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q25" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R25" s="20" t="str">
+        <x:v>Table 2; ageing=0 h; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S25" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T25" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U25" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V25" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W25" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X25" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="20" t="str">
+        <x:v>mirzaei2007-t2-age1-precursor</x:v>
+      </x:c>
+      <x:c r="B26" s="20" t="str">
+        <x:v>mirzaei2007-age1</x:v>
+      </x:c>
+      <x:c r="C26" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D26" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E26" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F26" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G26" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H26" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I26" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J26" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K26" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L26" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M26" s="20" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="N26" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O26" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P26" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q26" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R26" s="20" t="str">
+        <x:v>Table 2; ageing=1 h; precursor</x:v>
+      </x:c>
+      <x:c r="S26" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T26" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U26" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V26" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W26" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X26" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="20" t="str">
+        <x:v>mirzaei2007-t2-age1-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B27" s="20" t="str">
+        <x:v>mirzaei2007-age1</x:v>
+      </x:c>
+      <x:c r="C27" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D27" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E27" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F27" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G27" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H27" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I27" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K27" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L27" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M27" s="20" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="N27" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O27" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P27" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q27" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R27" s="20" t="str">
+        <x:v>Table 2; ageing=1 h; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S27" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T27" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U27" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V27" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W27" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X27" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="20" t="str">
+        <x:v>mirzaei2007-t2-age1-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B28" s="20" t="str">
+        <x:v>mirzaei2007-age1</x:v>
+      </x:c>
+      <x:c r="C28" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D28" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E28" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F28" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G28" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H28" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I28" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J28" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K28" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L28" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M28" s="20" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="N28" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O28" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P28" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q28" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R28" s="20" t="str">
+        <x:v>Table 2; ageing=1 h; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S28" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T28" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U28" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V28" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W28" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X28" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="20" t="str">
+        <x:v>mirzaei2007-t2-age2-precursor</x:v>
+      </x:c>
+      <x:c r="B29" s="20" t="str">
+        <x:v>mirzaei2007-age2</x:v>
+      </x:c>
+      <x:c r="C29" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D29" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E29" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F29" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G29" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H29" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I29" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J29" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K29" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L29" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M29" s="20" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N29" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O29" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P29" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q29" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R29" s="20" t="str">
+        <x:v>Table 2; ageing=2 h; precursor</x:v>
+      </x:c>
+      <x:c r="S29" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T29" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U29" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V29" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W29" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X29" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="20" t="str">
+        <x:v>mirzaei2007-t2-age2-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B30" s="20" t="str">
+        <x:v>mirzaei2007-age2</x:v>
+      </x:c>
+      <x:c r="C30" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D30" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E30" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F30" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G30" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H30" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I30" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J30" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K30" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L30" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M30" s="20" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N30" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O30" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P30" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q30" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R30" s="20" t="str">
+        <x:v>Table 2; ageing=2 h; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S30" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T30" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U30" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V30" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W30" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X30" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="20" t="str">
+        <x:v>mirzaei2007-t2-age2-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B31" s="20" t="str">
+        <x:v>mirzaei2007-age2</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D31" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E31" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F31" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G31" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H31" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I31" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J31" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K31" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L31" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M31" s="20" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="N31" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O31" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P31" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q31" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R31" s="20" t="str">
+        <x:v>Table 2; ageing=2 h; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S31" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T31" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U31" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V31" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W31" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X31" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="20" t="str">
+        <x:v>mirzaei2007-t2-age3-precursor</x:v>
+      </x:c>
+      <x:c r="B32" s="20" t="str">
+        <x:v>mirzaei2007-age3</x:v>
+      </x:c>
+      <x:c r="C32" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D32" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E32" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F32" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G32" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H32" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I32" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J32" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K32" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L32" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M32" s="20" t="n">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="N32" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O32" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P32" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q32" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R32" s="20" t="str">
+        <x:v>Table 2; ageing=3 h; precursor</x:v>
+      </x:c>
+      <x:c r="S32" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T32" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U32" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V32" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W32" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X32" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="20" t="str">
+        <x:v>mirzaei2007-t2-age3-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B33" s="20" t="str">
+        <x:v>mirzaei2007-age3</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D33" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E33" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F33" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G33" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H33" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I33" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J33" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K33" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L33" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M33" s="20" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N33" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O33" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P33" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q33" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R33" s="20" t="str">
+        <x:v>Table 2; ageing=3 h; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S33" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T33" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U33" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V33" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W33" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X33" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="20" t="str">
+        <x:v>mirzaei2007-t2-age3-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B34" s="20" t="str">
+        <x:v>mirzaei2007-age3</x:v>
+      </x:c>
+      <x:c r="C34" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D34" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E34" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F34" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G34" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H34" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I34" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J34" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K34" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L34" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M34" s="20" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="N34" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O34" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P34" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q34" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R34" s="20" t="str">
+        <x:v>Table 2; ageing=3 h; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S34" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T34" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U34" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V34" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W34" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X34" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="20" t="str">
+        <x:v>mirzaei2007-t2-age4-precursor</x:v>
+      </x:c>
+      <x:c r="B35" s="20" t="str">
+        <x:v>mirzaei2007-age4</x:v>
+      </x:c>
+      <x:c r="C35" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D35" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E35" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F35" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G35" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H35" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I35" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J35" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K35" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L35" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M35" s="20" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N35" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O35" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P35" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q35" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R35" s="20" t="str">
+        <x:v>Table 2; ageing=4 h; precursor</x:v>
+      </x:c>
+      <x:c r="S35" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T35" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U35" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V35" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W35" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X35" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="20" t="str">
+        <x:v>mirzaei2007-t2-age4-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B36" s="20" t="str">
+        <x:v>mirzaei2007-age4</x:v>
+      </x:c>
+      <x:c r="C36" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D36" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E36" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F36" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G36" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H36" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I36" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J36" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K36" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L36" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M36" s="20" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="N36" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O36" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P36" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q36" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R36" s="20" t="str">
+        <x:v>Table 2; ageing=4 h; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S36" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T36" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U36" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V36" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W36" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X36" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="20" t="str">
+        <x:v>mirzaei2007-t2-age4-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B37" s="20" t="str">
+        <x:v>mirzaei2007-age4</x:v>
+      </x:c>
+      <x:c r="C37" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D37" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E37" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F37" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G37" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H37" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I37" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J37" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K37" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L37" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M37" s="20" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="N37" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O37" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P37" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q37" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R37" s="20" t="str">
+        <x:v>Table 2; ageing=4 h; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S37" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T37" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U37" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V37" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W37" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X37" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="20" t="str">
+        <x:v>mirzaei2007-t2-age5-precursor</x:v>
+      </x:c>
+      <x:c r="B38" s="20" t="str">
+        <x:v>mirzaei2007-age5</x:v>
+      </x:c>
+      <x:c r="C38" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D38" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E38" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F38" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G38" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H38" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I38" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J38" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K38" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L38" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M38" s="20" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="N38" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O38" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P38" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q38" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R38" s="20" t="str">
+        <x:v>Table 2; ageing=5 h; precursor</x:v>
+      </x:c>
+      <x:c r="S38" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T38" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U38" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V38" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W38" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X38" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="20" t="str">
+        <x:v>mirzaei2007-t2-age5-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B39" s="20" t="str">
+        <x:v>mirzaei2007-age5</x:v>
+      </x:c>
+      <x:c r="C39" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D39" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E39" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F39" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G39" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H39" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I39" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J39" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K39" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L39" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M39" s="20" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="N39" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O39" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P39" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q39" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R39" s="20" t="str">
+        <x:v>Table 2; ageing=5 h; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S39" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T39" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U39" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V39" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W39" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X39" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="20" t="str">
+        <x:v>mirzaei2007-t2-age5-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B40" s="20" t="str">
+        <x:v>mirzaei2007-age5</x:v>
+      </x:c>
+      <x:c r="C40" s="20" t="str">
+        <x:v>mirzaei2007_table2</x:v>
+      </x:c>
+      <x:c r="D40" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20</x:v>
+      </x:c>
+      <x:c r="E40" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F40" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G40" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H40" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I40" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J40" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K40" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L40" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M40" s="20" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N40" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O40" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P40" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q40" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R40" s="20" t="str">
+        <x:v>Table 2; ageing=5 h; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S40" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T40" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U40" s="20" t="str">
+        <x:v>same_family_htft</x:v>
+      </x:c>
+      <x:c r="V40" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W40" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X40" s="20" t="str">
+        <x:v>Ageing-series BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="20" t="str">
+        <x:v>mirzaei2007-t3-15wt%SiO2-precursor</x:v>
+      </x:c>
+      <x:c r="B41" s="20" t="str">
+        <x:v>mirzaei2007-15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="C41" s="20" t="str">
+        <x:v>mirzaei2007_table3</x:v>
+      </x:c>
+      <x:c r="D41" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20_15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="E41" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F41" s="20" t="str">
+        <x:v>15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="G41" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H41" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I41" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J41" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K41" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L41" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M41" s="20" t="n">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="N41" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O41" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P41" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q41" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R41" s="20" t="str">
+        <x:v>Table 3; precursor</x:v>
+      </x:c>
+      <x:c r="S41" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T41" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U41" s="20" t="str">
+        <x:v>same_nominal_catalyst_htft</x:v>
+      </x:c>
+      <x:c r="V41" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W41" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X41" s="20" t="str">
+        <x:v>Support-comparison BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="20" t="str">
+        <x:v>mirzaei2007-t3-15wt%SiO2-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B42" s="20" t="str">
+        <x:v>mirzaei2007-15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="C42" s="20" t="str">
+        <x:v>mirzaei2007_table3</x:v>
+      </x:c>
+      <x:c r="D42" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20_15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="E42" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F42" s="20" t="str">
+        <x:v>15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="G42" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H42" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I42" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J42" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K42" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L42" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M42" s="20" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="N42" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O42" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P42" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q42" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R42" s="20" t="str">
+        <x:v>Table 3; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S42" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T42" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U42" s="20" t="str">
+        <x:v>same_nominal_catalyst_htft</x:v>
+      </x:c>
+      <x:c r="V42" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W42" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X42" s="20" t="str">
+        <x:v>Support-comparison BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="20" t="str">
+        <x:v>mirzaei2007-t3-15wt%SiO2-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B43" s="20" t="str">
+        <x:v>mirzaei2007-15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="C43" s="20" t="str">
+        <x:v>mirzaei2007_table3</x:v>
+      </x:c>
+      <x:c r="D43" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20_15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="E43" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F43" s="20" t="str">
+        <x:v>15wt%SiO2</x:v>
+      </x:c>
+      <x:c r="G43" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H43" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I43" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J43" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K43" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L43" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M43" s="20" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="N43" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O43" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P43" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q43" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R43" s="20" t="str">
+        <x:v>Table 3; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S43" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T43" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U43" s="20" t="str">
+        <x:v>same_nominal_catalyst_htft</x:v>
+      </x:c>
+      <x:c r="V43" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W43" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X43" s="20" t="str">
+        <x:v>Support-comparison BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="20" t="str">
+        <x:v>mirzaei2007-t3-none-precursor</x:v>
+      </x:c>
+      <x:c r="B44" s="20" t="str">
+        <x:v>mirzaei2007-none</x:v>
+      </x:c>
+      <x:c r="C44" s="20" t="str">
+        <x:v>mirzaei2007_table3</x:v>
+      </x:c>
+      <x:c r="D44" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20_none</x:v>
+      </x:c>
+      <x:c r="E44" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F44" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G44" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H44" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I44" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J44" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K44" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L44" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M44" s="20" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="N44" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O44" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P44" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q44" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R44" s="20" t="str">
+        <x:v>Table 3; precursor</x:v>
+      </x:c>
+      <x:c r="S44" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T44" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U44" s="20" t="str">
+        <x:v>same_nominal_catalyst_htft</x:v>
+      </x:c>
+      <x:c r="V44" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W44" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X44" s="20" t="str">
+        <x:v>Support-comparison BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="20" t="str">
+        <x:v>mirzaei2007-t3-none-calcined_before_test</x:v>
+      </x:c>
+      <x:c r="B45" s="20" t="str">
+        <x:v>mirzaei2007-none</x:v>
+      </x:c>
+      <x:c r="C45" s="20" t="str">
+        <x:v>mirzaei2007_table3</x:v>
+      </x:c>
+      <x:c r="D45" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20_none</x:v>
+      </x:c>
+      <x:c r="E45" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F45" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G45" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H45" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I45" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J45" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K45" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L45" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M45" s="20" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="N45" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O45" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P45" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q45" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R45" s="20" t="str">
+        <x:v>Table 3; calcined_before_test</x:v>
+      </x:c>
+      <x:c r="S45" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T45" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U45" s="20" t="str">
+        <x:v>same_nominal_catalyst_htft</x:v>
+      </x:c>
+      <x:c r="V45" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W45" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X45" s="20" t="str">
+        <x:v>Support-comparison BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="20" t="str">
+        <x:v>mirzaei2007-t3-none-calcined_after_test</x:v>
+      </x:c>
+      <x:c r="B46" s="20" t="str">
+        <x:v>mirzaei2007-none</x:v>
+      </x:c>
+      <x:c r="C46" s="20" t="str">
+        <x:v>mirzaei2007_table3</x:v>
+      </x:c>
+      <x:c r="D46" s="20" t="str">
+        <x:v>Mirzaei2007_Co80Ce20_none</x:v>
+      </x:c>
+      <x:c r="E46" s="20" t="str">
+        <x:v>80mol%Co/20mol%Ce</x:v>
+      </x:c>
+      <x:c r="F46" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G46" s="20" t="str">
+        <x:v>co-precipitation</x:v>
+      </x:c>
+      <x:c r="H46" s="20" t="n">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I46" s="20" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J46" s="20" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K46" s="20" t="n">
+        <x:v>4050</x:v>
+      </x:c>
+      <x:c r="L46" s="20" t="str">
+        <x:v>bet_surface_area</x:v>
+      </x:c>
+      <x:c r="M46" s="20" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="N46" s="20" t="str">
+        <x:v>m2_g</x:v>
+      </x:c>
+      <x:c r="O46" s="20" t="str">
+        <x:v>exact</x:v>
+      </x:c>
+      <x:c r="P46" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q46" s="20" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="R46" s="20" t="str">
+        <x:v>Table 3; calcined_after_test</x:v>
+      </x:c>
+      <x:c r="S46" s="20" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="T46" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U46" s="20" t="str">
+        <x:v>same_nominal_catalyst_htft</x:v>
+      </x:c>
+      <x:c r="V46" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W46" s="20" t="str">
+        <x:v>HTFT_and_not_independent</x:v>
+      </x:c>
+      <x:c r="X46" s="20" t="str">
+        <x:v>Support-comparison BET value</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="20" t="str">
+        <x:v>ernst1999-alpha-promoted-min</x:v>
+      </x:c>
+      <x:c r="B47" s="20" t="str">
+        <x:v>ernst1999-series</x:v>
+      </x:c>
+      <x:c r="C47" s="20" t="str">
+        <x:v>ernst1999_abstract</x:v>
+      </x:c>
+      <x:c r="D47" s="20" t="str">
+        <x:v>Ernst1999_CoCe_SiO2</x:v>
+      </x:c>
+      <x:c r="E47" s="20" t="str">
+        <x:v>25wt%Co;4.5-38.2wt%Ce</x:v>
+      </x:c>
+      <x:c r="F47" s="20" t="str">
+        <x:v>SiO2</x:v>
+      </x:c>
+      <x:c r="G47" s="20" t="str">
+        <x:v>oxalate_coprecipitation_TEOS</x:v>
+      </x:c>
+      <x:c r="H47" s="20" t="n">
+        <x:v>219.85</x:v>
+      </x:c>
+      <x:c r="I47" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J47" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K47" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L47" s="20" t="str">
+        <x:v>alpha_chain_growth</x:v>
+      </x:c>
+      <x:c r="M47" s="20" t="n">
+        <x:v>0.82</x:v>
+      </x:c>
+      <x:c r="N47" s="20" t="str">
+        <x:v>fraction</x:v>
+      </x:c>
+      <x:c r="O47" s="20" t="str">
+        <x:v>range_min</x:v>
+      </x:c>
+      <x:c r="P47" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q47" s="20" t="str">
+        <x:v>Ernst et al. (1999)</x:v>
+      </x:c>
+      <x:c r="R47" s="20" t="str">
+        <x:v>Abstract</x:v>
+      </x:c>
+      <x:c r="S47" s="20" t="str">
+        <x:v>https://doi.org/10.1016/S0920-5861(98)00519-7</x:v>
+      </x:c>
+      <x:c r="T47" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U47" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V47" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W47" s="20" t="str">
+        <x:v>composition_pressure_preparation_mismatch</x:v>
+      </x:c>
+      <x:c r="X47" s="20" t="str">
+        <x:v>Lower end of reported alpha range for Ce-containing catalysts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="20" t="str">
+        <x:v>ernst1999-alpha-promoted-max</x:v>
+      </x:c>
+      <x:c r="B48" s="20" t="str">
+        <x:v>ernst1999-series</x:v>
+      </x:c>
+      <x:c r="C48" s="20" t="str">
+        <x:v>ernst1999_abstract</x:v>
+      </x:c>
+      <x:c r="D48" s="20" t="str">
+        <x:v>Ernst1999_CoCe_SiO2</x:v>
+      </x:c>
+      <x:c r="E48" s="20" t="str">
+        <x:v>25wt%Co;4.5-38.2wt%Ce</x:v>
+      </x:c>
+      <x:c r="F48" s="20" t="str">
+        <x:v>SiO2</x:v>
+      </x:c>
+      <x:c r="G48" s="20" t="str">
+        <x:v>oxalate_coprecipitation_TEOS</x:v>
+      </x:c>
+      <x:c r="H48" s="20" t="n">
+        <x:v>219.85</x:v>
+      </x:c>
+      <x:c r="I48" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J48" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K48" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L48" s="20" t="str">
+        <x:v>alpha_chain_growth</x:v>
+      </x:c>
+      <x:c r="M48" s="20" t="n">
+        <x:v>0.87</x:v>
+      </x:c>
+      <x:c r="N48" s="20" t="str">
+        <x:v>fraction</x:v>
+      </x:c>
+      <x:c r="O48" s="20" t="str">
+        <x:v>range_max</x:v>
+      </x:c>
+      <x:c r="P48" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q48" s="20" t="str">
+        <x:v>Ernst et al. (1999)</x:v>
+      </x:c>
+      <x:c r="R48" s="20" t="str">
+        <x:v>Abstract</x:v>
+      </x:c>
+      <x:c r="S48" s="20" t="str">
+        <x:v>https://doi.org/10.1016/S0920-5861(98)00519-7</x:v>
+      </x:c>
+      <x:c r="T48" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U48" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V48" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W48" s="20" t="str">
+        <x:v>composition_pressure_preparation_mismatch</x:v>
+      </x:c>
+      <x:c r="X48" s="20" t="str">
+        <x:v>Upper end of reported alpha range for Ce-containing catalysts</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="20" t="str">
+        <x:v>ernst1999-alpha-unpromoted</x:v>
+      </x:c>
+      <x:c r="B49" s="20" t="str">
+        <x:v>ernst1999-unpromoted</x:v>
+      </x:c>
+      <x:c r="C49" s="20" t="str">
+        <x:v>ernst1999_abstract</x:v>
+      </x:c>
+      <x:c r="D49" s="20" t="str">
+        <x:v>Ernst1999_Co_SiO2</x:v>
+      </x:c>
+      <x:c r="E49" s="20" t="str">
+        <x:v>25wt%Co</x:v>
+      </x:c>
+      <x:c r="F49" s="20" t="str">
+        <x:v>SiO2</x:v>
+      </x:c>
+      <x:c r="G49" s="20" t="str">
+        <x:v>reference_preparation</x:v>
+      </x:c>
+      <x:c r="H49" s="20" t="n">
+        <x:v>219.85</x:v>
+      </x:c>
+      <x:c r="I49" s="20" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J49" s="20" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K49" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L49" s="20" t="str">
+        <x:v>alpha_chain_growth</x:v>
+      </x:c>
+      <x:c r="M49" s="20" t="n">
+        <x:v>0.92</x:v>
+      </x:c>
+      <x:c r="N49" s="20" t="str">
+        <x:v>fraction</x:v>
+      </x:c>
+      <x:c r="O49" s="20" t="str">
+        <x:v>exact_as_reported</x:v>
+      </x:c>
+      <x:c r="P49" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q49" s="20" t="str">
+        <x:v>Ernst et al. (1999)</x:v>
+      </x:c>
+      <x:c r="R49" s="20" t="str">
+        <x:v>Abstract</x:v>
+      </x:c>
+      <x:c r="S49" s="20" t="str">
+        <x:v>https://doi.org/10.1016/S0920-5861(98)00519-7</x:v>
+      </x:c>
+      <x:c r="T49" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U49" s="20" t="str">
+        <x:v>independent_LTFT_reference_catalyst</x:v>
+      </x:c>
+      <x:c r="V49" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W49" s="20" t="str">
+        <x:v>no_ceria_and_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X49" s="20" t="str">
+        <x:v>Unpromoted reference catalyst</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="20" t="str">
+        <x:v>bruce1993-activity-multiplier</x:v>
+      </x:c>
+      <x:c r="B50" s="20" t="str">
+        <x:v>bruce1993-ru03</x:v>
+      </x:c>
+      <x:c r="C50" s="20" t="str">
+        <x:v>bruce1993_abstract</x:v>
+      </x:c>
+      <x:c r="D50" s="20" t="str">
+        <x:v>Bruce1993_Ru_CoCe</x:v>
+      </x:c>
+      <x:c r="E50" s="20" t="str">
+        <x:v>Co/Ce+0.3wt%Ru</x:v>
+      </x:c>
+      <x:c r="F50" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G50" s="20" t="str">
+        <x:v>co-precipitation_plus_Ru_adsorption</x:v>
+      </x:c>
+      <x:c r="H50" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="I50" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="J50" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K50" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L50" s="20" t="str">
+        <x:v>relative_activity_multiplier</x:v>
+      </x:c>
+      <x:c r="M50" s="20" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="N50" s="20" t="str">
+        <x:v>fold</x:v>
+      </x:c>
+      <x:c r="O50" s="20" t="str">
+        <x:v>approximate</x:v>
+      </x:c>
+      <x:c r="P50" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q50" s="20" t="str">
+        <x:v>Bruce et al. (1993)</x:v>
+      </x:c>
+      <x:c r="R50" s="20" t="str">
+        <x:v>Abstract</x:v>
+      </x:c>
+      <x:c r="S50" s="20" t="str">
+        <x:v>https://doi.org/10.1016/0926-860X(93)80115-7</x:v>
+      </x:c>
+      <x:c r="T50" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U50" s="20" t="str">
+        <x:v>independent_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V50" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W50" s="20" t="str">
+        <x:v>support_promoter_domain_mismatch</x:v>
+      </x:c>
+      <x:c r="X50" s="20" t="str">
+        <x:v>Activity described as trebled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="20" t="str">
+        <x:v>bruce1993-conversion-lower-bound</x:v>
+      </x:c>
+      <x:c r="B51" s="20" t="str">
+        <x:v>bruce1993-stability</x:v>
+      </x:c>
+      <x:c r="C51" s="20" t="str">
+        <x:v>bruce1993_abstract</x:v>
+      </x:c>
+      <x:c r="D51" s="20" t="str">
+        <x:v>Bruce1993_Ru_CoCe</x:v>
+      </x:c>
+      <x:c r="E51" s="20" t="str">
+        <x:v>Co/Ce+0.3wt%Ru</x:v>
+      </x:c>
+      <x:c r="F51" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G51" s="20" t="str">
+        <x:v>co-precipitation_plus_Ru_adsorption</x:v>
+      </x:c>
+      <x:c r="H51" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="I51" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="J51" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K51" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L51" s="20" t="str">
+        <x:v>conversion_co_pct</x:v>
+      </x:c>
+      <x:c r="M51" s="20" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="N51" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O51" s="20" t="str">
+        <x:v>lower_bound_exclusive</x:v>
+      </x:c>
+      <x:c r="P51" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q51" s="20" t="str">
+        <x:v>Bruce et al. (1993)</x:v>
+      </x:c>
+      <x:c r="R51" s="20" t="str">
+        <x:v>Abstract</x:v>
+      </x:c>
+      <x:c r="S51" s="20" t="str">
+        <x:v>https://doi.org/10.1016/0926-860X(93)80115-7</x:v>
+      </x:c>
+      <x:c r="T51" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U51" s="20" t="str">
+        <x:v>independent_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V51" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W51" s="20" t="str">
+        <x:v>support_promoter_domain_mismatch</x:v>
+      </x:c>
+      <x:c r="X51" s="20" t="str">
+        <x:v>Published wording: conversion over 40%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="20" t="str">
+        <x:v>bruce1993-stability-duration</x:v>
+      </x:c>
+      <x:c r="B52" s="20" t="str">
+        <x:v>bruce1993-stability</x:v>
+      </x:c>
+      <x:c r="C52" s="20" t="str">
+        <x:v>bruce1993_abstract</x:v>
+      </x:c>
+      <x:c r="D52" s="20" t="str">
+        <x:v>Bruce1993_Ru_CoCe</x:v>
+      </x:c>
+      <x:c r="E52" s="20" t="str">
+        <x:v>Co/Ce+0.3wt%Ru</x:v>
+      </x:c>
+      <x:c r="F52" s="20" t="str">
+        <x:v>none</x:v>
+      </x:c>
+      <x:c r="G52" s="20" t="str">
+        <x:v>co-precipitation_plus_Ru_adsorption</x:v>
+      </x:c>
+      <x:c r="H52" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="I52" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="J52" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K52" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L52" s="20" t="str">
+        <x:v>stable_time_on_stream</x:v>
+      </x:c>
+      <x:c r="M52" s="20" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="N52" s="20" t="str">
+        <x:v>h</x:v>
+      </x:c>
+      <x:c r="O52" s="20" t="str">
+        <x:v>upper_duration_reported</x:v>
+      </x:c>
+      <x:c r="P52" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q52" s="20" t="str">
+        <x:v>Bruce et al. (1993)</x:v>
+      </x:c>
+      <x:c r="R52" s="20" t="str">
+        <x:v>Abstract</x:v>
+      </x:c>
+      <x:c r="S52" s="20" t="str">
+        <x:v>https://doi.org/10.1016/0926-860X(93)80115-7</x:v>
+      </x:c>
+      <x:c r="T52" s="20" t="str">
+        <x:v>published_experiment</x:v>
+      </x:c>
+      <x:c r="U52" s="20" t="str">
+        <x:v>independent_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V52" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W52" s="20" t="str">
+        <x:v>support_promoter_domain_mismatch</x:v>
+      </x:c>
+      <x:c r="X52" s="20" t="str">
+        <x:v>Activity maintained almost unchanged for periods up to 100 h</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="20" t="str">
+        <x:v>macheli2014-max-activity-improvement</x:v>
+      </x:c>
+      <x:c r="B53" s="20" t="str">
+        <x:v>macheli2014-model-series</x:v>
+      </x:c>
+      <x:c r="C53" s="20" t="str">
+        <x:v>macheli2014_thesis_abstract</x:v>
+      </x:c>
+      <x:c r="D53" s="20" t="str">
+        <x:v>Macheli2014_Co3O4_SiO2</x:v>
+      </x:c>
+      <x:c r="E53" s="20" t="str">
+        <x:v>Co3O4 nanocubes modified with SiO2</x:v>
+      </x:c>
+      <x:c r="F53" s="20" t="str">
+        <x:v>SiO2_surface_modification</x:v>
+      </x:c>
+      <x:c r="G53" s="20" t="str">
+        <x:v>oxidative_precipitation_plus_TEOS</x:v>
+      </x:c>
+      <x:c r="H53" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="I53" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="J53" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K53" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L53" s="20" t="str">
+        <x:v>relative_activity_multiplier</x:v>
+      </x:c>
+      <x:c r="M53" s="20" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="N53" s="20" t="str">
+        <x:v>fold</x:v>
+      </x:c>
+      <x:c r="O53" s="20" t="str">
+        <x:v>approximate_max</x:v>
+      </x:c>
+      <x:c r="P53" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q53" s="20" t="str">
+        <x:v>Macheli (2014), MSc thesis</x:v>
+      </x:c>
+      <x:c r="R53" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S53" s="20" t="str">
+        <x:v>https://open.uct.ac.za/items/58fe53ab-267b-431a-a2a8-89ac1e5c752b</x:v>
+      </x:c>
+      <x:c r="T53" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U53" s="20" t="str">
+        <x:v>independent_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V53" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W53" s="20" t="str">
+        <x:v>no_ceria_and_model_architecture</x:v>
+      </x:c>
+      <x:c r="X53" s="20" t="str">
+        <x:v>Repository abstract reports maximum activity improvement of about 15 times</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="20" t="str">
+        <x:v>chikati2023-minus53_plus38-conversion</x:v>
+      </x:c>
+      <x:c r="B54" s="20" t="str">
+        <x:v>chikati2023-minus53_plus38</x:v>
+      </x:c>
+      <x:c r="C54" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D54" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E54" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F54" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G54" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H54" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I54" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J54" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K54" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L54" s="20" t="str">
+        <x:v>conversion_co_pct</x:v>
+      </x:c>
+      <x:c r="M54" s="20" t="n">
+        <x:v>44.97</x:v>
+      </x:c>
+      <x:c r="N54" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O54" s="20" t="str">
+        <x:v>exact_as_reported</x:v>
+      </x:c>
+      <x:c r="P54" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q54" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R54" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S54" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T54" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U54" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V54" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W54" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X54" s="20" t="str">
+        <x:v>Support particle class minus53_plus38</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="20" t="str">
+        <x:v>chikati2023-minus78_plus53-conversion</x:v>
+      </x:c>
+      <x:c r="B55" s="20" t="str">
+        <x:v>chikati2023-minus78_plus53</x:v>
+      </x:c>
+      <x:c r="C55" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D55" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E55" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F55" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G55" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H55" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I55" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J55" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K55" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L55" s="20" t="str">
+        <x:v>conversion_co_pct</x:v>
+      </x:c>
+      <x:c r="M55" s="20" t="n">
+        <x:v>32.06</x:v>
+      </x:c>
+      <x:c r="N55" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O55" s="20" t="str">
+        <x:v>exact_as_reported</x:v>
+      </x:c>
+      <x:c r="P55" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q55" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R55" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S55" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T55" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U55" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V55" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W55" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X55" s="20" t="str">
+        <x:v>Support particle class minus78_plus53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="20" t="str">
+        <x:v>chikati2023-lt25-conversion</x:v>
+      </x:c>
+      <x:c r="B56" s="20" t="str">
+        <x:v>chikati2023-lt25</x:v>
+      </x:c>
+      <x:c r="C56" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D56" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E56" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F56" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G56" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H56" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I56" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J56" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K56" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L56" s="20" t="str">
+        <x:v>conversion_co_pct</x:v>
+      </x:c>
+      <x:c r="M56" s="20" t="n">
+        <x:v>31.29</x:v>
+      </x:c>
+      <x:c r="N56" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O56" s="20" t="str">
+        <x:v>exact_as_reported</x:v>
+      </x:c>
+      <x:c r="P56" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q56" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R56" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S56" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T56" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U56" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V56" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W56" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X56" s="20" t="str">
+        <x:v>Support particle class lt25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="20" t="str">
+        <x:v>chikati2023-selectivity_ch4_pct-min</x:v>
+      </x:c>
+      <x:c r="B57" s="20" t="str">
+        <x:v>chikati2023-range</x:v>
+      </x:c>
+      <x:c r="C57" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D57" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E57" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F57" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G57" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H57" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I57" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J57" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K57" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L57" s="20" t="str">
+        <x:v>selectivity_ch4_pct</x:v>
+      </x:c>
+      <x:c r="M57" s="20" t="n">
+        <x:v>14.95</x:v>
+      </x:c>
+      <x:c r="N57" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O57" s="20" t="str">
+        <x:v>range_min</x:v>
+      </x:c>
+      <x:c r="P57" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q57" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R57" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S57" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T57" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U57" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V57" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W57" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X57" s="20" t="str">
+        <x:v>Range across support particle-size classes; not paired to a single run</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="20" t="str">
+        <x:v>chikati2023-selectivity_ch4_pct-max</x:v>
+      </x:c>
+      <x:c r="B58" s="20" t="str">
+        <x:v>chikati2023-range</x:v>
+      </x:c>
+      <x:c r="C58" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D58" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E58" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F58" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G58" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H58" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I58" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J58" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K58" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L58" s="20" t="str">
+        <x:v>selectivity_ch4_pct</x:v>
+      </x:c>
+      <x:c r="M58" s="20" t="n">
+        <x:v>16.97</x:v>
+      </x:c>
+      <x:c r="N58" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O58" s="20" t="str">
+        <x:v>range_max</x:v>
+      </x:c>
+      <x:c r="P58" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q58" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R58" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S58" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T58" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U58" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V58" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W58" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X58" s="20" t="str">
+        <x:v>Range across support particle-size classes; not paired to a single run</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="20" t="str">
+        <x:v>chikati2023-selectivity_c2_c4_pct-min</x:v>
+      </x:c>
+      <x:c r="B59" s="20" t="str">
+        <x:v>chikati2023-range</x:v>
+      </x:c>
+      <x:c r="C59" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D59" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E59" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F59" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G59" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H59" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I59" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J59" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K59" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L59" s="20" t="str">
+        <x:v>selectivity_c2_c4_pct</x:v>
+      </x:c>
+      <x:c r="M59" s="20" t="n">
+        <x:v>14.55</x:v>
+      </x:c>
+      <x:c r="N59" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O59" s="20" t="str">
+        <x:v>range_min</x:v>
+      </x:c>
+      <x:c r="P59" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q59" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R59" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S59" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T59" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U59" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V59" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W59" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X59" s="20" t="str">
+        <x:v>Range across support particle-size classes; not paired to a single run</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="20" t="str">
+        <x:v>chikati2023-selectivity_c2_c4_pct-max</x:v>
+      </x:c>
+      <x:c r="B60" s="20" t="str">
+        <x:v>chikati2023-range</x:v>
+      </x:c>
+      <x:c r="C60" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D60" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E60" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F60" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G60" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H60" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I60" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J60" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K60" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L60" s="20" t="str">
+        <x:v>selectivity_c2_c4_pct</x:v>
+      </x:c>
+      <x:c r="M60" s="20" t="n">
+        <x:v>19.01</x:v>
+      </x:c>
+      <x:c r="N60" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O60" s="20" t="str">
+        <x:v>range_max</x:v>
+      </x:c>
+      <x:c r="P60" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q60" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R60" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S60" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T60" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U60" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V60" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W60" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X60" s="20" t="str">
+        <x:v>Range across support particle-size classes; not paired to a single run</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="20" t="str">
+        <x:v>chikati2023-selectivity_c5plus_pct-min</x:v>
+      </x:c>
+      <x:c r="B61" s="20" t="str">
+        <x:v>chikati2023-range</x:v>
+      </x:c>
+      <x:c r="C61" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D61" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E61" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F61" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G61" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H61" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I61" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J61" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K61" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L61" s="20" t="str">
+        <x:v>selectivity_c5plus_pct</x:v>
+      </x:c>
+      <x:c r="M61" s="20" t="n">
+        <x:v>66.04</x:v>
+      </x:c>
+      <x:c r="N61" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O61" s="20" t="str">
+        <x:v>range_min</x:v>
+      </x:c>
+      <x:c r="P61" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q61" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R61" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S61" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T61" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U61" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V61" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W61" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X61" s="20" t="str">
+        <x:v>Range across support particle-size classes; not paired to a single run</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="20" t="str">
+        <x:v>chikati2023-selectivity_c5plus_pct-max</x:v>
+      </x:c>
+      <x:c r="B62" s="20" t="str">
+        <x:v>chikati2023-range</x:v>
+      </x:c>
+      <x:c r="C62" s="20" t="str">
+        <x:v>chikati2023_repository_abstract</x:v>
+      </x:c>
+      <x:c r="D62" s="20" t="str">
+        <x:v>Chikati2023_Co_clinoptilolite</x:v>
+      </x:c>
+      <x:c r="E62" s="20" t="str">
+        <x:v>10wt%Co</x:v>
+      </x:c>
+      <x:c r="F62" s="20" t="str">
+        <x:v>clinoptilolite</x:v>
+      </x:c>
+      <x:c r="G62" s="20" t="str">
+        <x:v>incipient_wetness_impregnation</x:v>
+      </x:c>
+      <x:c r="H62" s="20" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="I62" s="20" t="n">
+        <x:v>10.85</x:v>
+      </x:c>
+      <x:c r="J62" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="K62" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="L62" s="20" t="str">
+        <x:v>selectivity_c5plus_pct</x:v>
+      </x:c>
+      <x:c r="M62" s="20" t="n">
+        <x:v>70.29</x:v>
+      </x:c>
+      <x:c r="N62" s="20" t="str">
+        <x:v>pct</x:v>
+      </x:c>
+      <x:c r="O62" s="20" t="str">
+        <x:v>range_max</x:v>
+      </x:c>
+      <x:c r="P62" s="20" t="str">
+        <x:v>not_reported</x:v>
+      </x:c>
+      <x:c r="Q62" s="20" t="str">
+        <x:v>Chikati (2023), PhD thesis</x:v>
+      </x:c>
+      <x:c r="R62" s="20" t="str">
+        <x:v>Repository abstract</x:v>
+      </x:c>
+      <x:c r="S62" s="20" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="T62" s="20" t="str">
+        <x:v>thesis_abstract</x:v>
+      </x:c>
+      <x:c r="U62" s="20" t="str">
+        <x:v>independent_LTFT_different_catalyst</x:v>
+      </x:c>
+      <x:c r="V62" s="21" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="W62" s="20" t="str">
+        <x:v>support_composition_pressure_mismatch</x:v>
+      </x:c>
+      <x:c r="X62" s="20" t="str">
+        <x:v>Range across support particle-size classes; not paired to a single run</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f1f6218511244dd"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="32" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="30" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="22" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="22" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="42" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="25" t="str">
+        <x:v>source_id</x:v>
+      </x:c>
+      <x:c r="B1" s="25" t="str">
+        <x:v>reference</x:v>
+      </x:c>
+      <x:c r="C1" s="25" t="str">
+        <x:v>document_type</x:v>
+      </x:c>
+      <x:c r="D1" s="25" t="str">
+        <x:v>institution_or_journal</x:v>
+      </x:c>
+      <x:c r="E1" s="25" t="str">
+        <x:v>catalyst_scope</x:v>
+      </x:c>
+      <x:c r="F1" s="25" t="str">
+        <x:v>numeric_extraction_status</x:v>
+      </x:c>
+      <x:c r="G1" s="25" t="str">
+        <x:v>included_measurements</x:v>
+      </x:c>
+      <x:c r="H1" s="25" t="str">
+        <x:v>priority</x:v>
+      </x:c>
+      <x:c r="I1" s="25" t="str">
+        <x:v>validation_role</x:v>
+      </x:c>
+      <x:c r="J1" s="25" t="str">
+        <x:v>source_url</x:v>
+      </x:c>
+      <x:c r="K1" s="25" t="str">
+        <x:v>note</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
+        <x:v>mansouri2013</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>Mansouri et al. (2013)</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>article</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>International Journal of Industrial Chemistry</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>exact Co-Ce/SiO2 catalyst</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>complete_existing</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="n">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="str">
+        <x:v>core</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
+        <x:v>calibration_only</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str">
+        <x:v>https://doi.org/10.1186/2228-5547-4-1</x:v>
+      </x:c>
+      <x:c r="K2" s="11" t="str">
+        <x:v>Already present in main measurements table</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>lari2017</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>Taherzadeh Lari et al. (2017)</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>article+supplement</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>RSC Advances</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>Fe-Co-Ce nanocatalysts</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>complete_existing</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="n">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="str">
+        <x:v>contextual</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str">
+        <x:v>trend_only</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str">
+        <x:v>https://doi.org/10.1039/C7RA05490D</x:v>
+      </x:c>
+      <x:c r="K3" s="11" t="str">
+        <x:v>Already present in main measurements table</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>mirzaei2007</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Mirzaei et al. (2007)</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>article</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>Journal of the Iranian Chemical Society</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>Co-Ce and supported Co-Ce screening</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>partial_tables</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str">
+        <x:v>preparation_characterization</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str">
+        <x:v>https://doi.org/10.1007/BF03245986</x:v>
+      </x:c>
+      <x:c r="K4" s="11" t="str">
+        <x:v>BET Tables 1-3 integrated; conversion/selectivity remain graph-only</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>ernst1999</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Ernst et al. (1999)</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>article</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Catalysis Today</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>25wt%Co with 4.5-38.2wt%Ce on SiO2</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>partial_abstract</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>independent_LTFT_trend</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str">
+        <x:v>https://doi.org/10.1016/S0920-5861(98)00519-7</x:v>
+      </x:c>
+      <x:c r="K5" s="11" t="str">
+        <x:v>Alpha values integrated; full tables pending</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>bruce1993</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>Bruce et al. (1993)</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>article</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Applied Catalysis A</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Ru-promoted coprecipitated Co/Ce</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>partial_abstract</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>independent_context</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
+        <x:v>https://doi.org/10.1016/0926-860X(93)80115-7</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="str">
+        <x:v>Bounds and relative statements retained with qualifiers</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
+        <x:v>dai2006</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>Dai et al. (2006)</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>article</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>Chinese Journal of Catalysis</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>CeO2-promoted Co/SiO2</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>no_explicit_numeric_yet</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="str">
+        <x:v>mechanistic_context</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str">
+        <x:v>https://doi.org/10.1016/S1872-2067(06)60047-8</x:v>
+      </x:c>
+      <x:c r="K7" s="11" t="str">
+        <x:v>Full tables require extraction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
+        <x:v>arsalanfar2012</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>Arsalanfar et al. (2012)</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>article</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>Journal of Natural Gas Science and Engineering</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>supported Co-Ce characterization</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>no_new_numeric_yet</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
+        <x:v>characterization_context</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>https://doi.org/10.1016/j.jngse.2012.05.015</x:v>
+      </x:c>
+      <x:c r="K8" s="11" t="str">
+        <x:v>Overlaps scientific lineage; full tables require extraction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>beigbabaei2010</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>Beigbabaei et al. (2010)</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>article</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>Open Catalysis Journal</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>fusion-prepared Co/CeO2/SiO2</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>graph_only_not_digitized</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>HTFT_context</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str"/>
+      <x:c r="K9" s="11" t="str">
+        <x:v>No automatic digitization without uncertainty protocol</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>menezes2018</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Menezes (2018)</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>master_thesis</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>UFC</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>Co/SBA-15 and Co/Ru/MCM-41</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>conditions_only</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
+        <x:v>independent_LTFT_trend</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str">
+        <x:v>https://repositorio.ufc.br/handle/riufc/31542</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="str">
+        <x:v>Tables in PDF pending structured extraction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>shiba2021</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>Shiba (2021)</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>doctoral_thesis</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>UNISA</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>Co/SiO2, Co/TiO2, Co/Al2O3, Co-Ru</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>conditions_only</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>activation_and_phase_trend</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str">
+        <x:v>https://hdl.handle.net/10500/28804</x:v>
+      </x:c>
+      <x:c r="K11" s="11" t="str">
+        <x:v>Tables in PDF pending structured extraction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>mathe2021</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>Mathe (2021)</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>master_thesis</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>University of Cape Town</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>Mn-promoted 22wt%Co/SiO2</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>conditions_only</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str">
+        <x:v>independent_LTFT_trend</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="str">
+        <x:v>http://hdl.handle.net/11427/35863</x:v>
+      </x:c>
+      <x:c r="K12" s="11" t="str">
+        <x:v>Tables in PDF pending structured extraction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="str">
+        <x:v>chikati2023</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>Chikati (2023)</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>doctoral_thesis</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>University of the Witwatersrand</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>10wt%Co/clinoptilolite</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>partial_abstract</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str">
+        <x:v>high</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>independent_LTFT_trend</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="str">
+        <x:v>https://hdl.handle.net/10539/37372</x:v>
+      </x:c>
+      <x:c r="K13" s="11" t="str">
+        <x:v>Conversions and selectivity ranges integrated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="str">
+        <x:v>rodrigues2015</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>Rodrigues (2015)</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>doctoral_thesis</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>UFCG</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str">
+        <x:v>Co/SBA-15 and Ru/Co/SBA-15</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>conditions_only</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="str">
+        <x:v>support_promoter_trend</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str">
+        <x:v>https://dspace.sti.ufcg.edu.br/handle/riufcg/317</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="str">
+        <x:v>Tables in PDF pending structured extraction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11" t="str">
+        <x:v>smarzaro2022</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>Smarzaro (2022)</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>doctoral_thesis</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>UFRJ/COPPE</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>silica/carbon-encapsulated Co nanoparticles</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="str">
+        <x:v>conditions_only</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str">
+        <x:v>architecture_trend</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="str">
+        <x:v>https://bdtd.ibict.br/vufind/Record/UFRJ_16837840926cfd85d46619b991556778</x:v>
+      </x:c>
+      <x:c r="K15" s="11" t="str">
+        <x:v>Tables in PDF pending structured extraction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="11" t="str">
+        <x:v>ribeiro2016</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>Ribeiro (2016)</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>master_thesis</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>UFPE</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str">
+        <x:v>modified cobalt catalysts</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
+        <x:v>conditions_only</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str">
+        <x:v>preparation_trend</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="str">
+        <x:v>https://repositorio.ufpe.br/handle/123456789/25099</x:v>
+      </x:c>
+      <x:c r="K16" s="11" t="str">
+        <x:v>Tables in PDF pending structured extraction</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="11" t="str">
+        <x:v>macheli2014</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>Macheli (2014)</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>master_thesis</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>University of Cape Town</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>SiO2-modified Co3O4 nanocubes</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>partial_abstract</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="str">
+        <x:v>medium</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="str">
+        <x:v>metal_support_context</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="str">
+        <x:v>https://open.uct.ac.za/items/58fe53ab-267b-431a-a2a8-89ac1e5c752b</x:v>
+      </x:c>
+      <x:c r="K17" s="11" t="str">
+        <x:v>Approximate maximum activity multiplier integrated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="11" t="str">
+        <x:v>barros2013</x:v>
+      </x:c>
+      <x:c r="B18" s="11" t="str">
+        <x:v>Barros Junior (2013)</x:v>
+      </x:c>
+      <x:c r="C18" s="11" t="str">
+        <x:v>doctoral_thesis</x:v>
+      </x:c>
+      <x:c r="D18" s="11" t="str">
+        <x:v>UFC</x:v>
+      </x:c>
+      <x:c r="E18" s="11" t="str">
+        <x:v>cobalt fixed-bed reactor model</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="str">
+        <x:v>modeling_only</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" s="11" t="str">
+        <x:v>low</x:v>
+      </x:c>
+      <x:c r="I18" s="11" t="str">
+        <x:v>model_methodology</x:v>
+      </x:c>
+      <x:c r="J18" s="11" t="str">
+        <x:v>https://repositorio.ufc.br/handle/riufc/4835</x:v>
+      </x:c>
+      <x:c r="K18" s="11" t="str">
+        <x:v>Not an external catalyst-validation dataset</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3fbd9fbf05b4dc2"/>
+  </x:tableParts>
+</x:worksheet>
 </file>